--- a/docs/checklist-nonfunctional.xlsx
+++ b/docs/checklist-nonfunctional.xlsx
@@ -1,46 +1,149 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Нефункциональный чек-лист" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Нефункциональный чек-лист" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+  <si>
+    <t>№</t>
+  </si>
+  <si>
+    <t>Категория</t>
+  </si>
+  <si>
+    <t>Проверка</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>UI/UX</t>
+  </si>
+  <si>
+    <t>Интерфейс корректно отображается в разрешении 1920×1080, без горизонтальной прокрутки</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Названия элементов и подписи полей понятны и не обрезаются</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Сообщения об ошибках валидации отображаются рядом с полем и понятны пользователю</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Интерактивные элементы (кнопки, ссылки, карточки) имеют состояние при наведении курсора</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Навигация по разделам приложения интуитивна (дашборд → проект → доска → задача)</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Кросс-браузерность</t>
+  </si>
+  <si>
+    <t>Ключевые сценарии (вход, создание проекта, создание задачи) работают в Microsoft Edge</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Ключевые сценарии работают в Google Chrome</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Ключевые сценарии работают в Mozilla Firefox</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Вёрстка не «плывёт» при изменении размера окна браузера (адаптивность базовых макетов)</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Доступность</t>
+  </si>
+  <si>
+    <t>По интерфейсу можно перемещаться с клавиатуры (Tab, Enter, Escape)</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Поля ввода имеют текстовые подписи (label)</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Кнопки и ссылки имеют осмысленные названия для программ чтения с экрана</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Контраст текста относительно фона достаточен для чтения</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF6C5CE7"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,103 +157,35 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -438,232 +473,169 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="3" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Категория</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>UI/UX</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Интерфейс корректно отображается в разрешении 1920×1080, без горизонтальной прокрутки</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>UI/UX</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Названия элементов и подписи полей понятны и не обрезаются</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>UI/UX</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Сообщения об ошибках валидации отображаются рядом с полем и понятны пользователю</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>UI/UX</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Интерактивные элементы (кнопки, ссылки, карточки) имеют состояние при наведении курсора</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>UI/UX</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Навигация по разделам приложения интуитивна (дашборд → проект → доска → задача)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Кросс-браузерность</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Ключевые сценарии (вход, создание проекта, создание задачи) работают в Microsoft Edge</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Кросс-браузерность</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Ключевые сценарии работают в Google Chrome</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Кросс-браузерность</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Ключевые сценарии работают в Mozilla Firefox</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Кросс-браузерность</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Вёрстка не «плывёт» при изменении размера окна браузера (адаптивность базовых макетов)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Доступность</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>По интерфейсу можно перемещаться с клавиатуры (Tab, Enter, Escape)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Доступность</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Поля ввода имеют текстовые подписи (label)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Доступность</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Кнопки и ссылки имеют осмысленные названия для программ чтения с экрана</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Доступность</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Контраст текста относительно фона достаточен для чтения</t>
-        </is>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>